--- a/Manual testing.xlsx
+++ b/Manual testing.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Praveena\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Praveena\SauceDemo manual testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9E6B81F-EC80-4E9B-839C-749F643B7542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAEDB733-53F4-4FF2-8A27-F9A7BFF2334E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{3FE13B07-3634-45D3-A178-EF13760B6945}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="129">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -446,12 +446,115 @@
   <si>
     <t xml:space="preserve">user was return to the previous page </t>
   </si>
+  <si>
+    <t>An Error message should be displayed.
+“Username and Password are required”</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test data </t>
+  </si>
+  <si>
+    <t>Username : standard_user
+Password : secret_sauce</t>
+  </si>
+  <si>
+    <t>Username : standard_user
+Password : 123</t>
+  </si>
+  <si>
+    <t>Username : user
+Password : secret_sauce</t>
+  </si>
+  <si>
+    <t>Username : user
+Password :123</t>
+  </si>
+  <si>
+    <t>Username : (blank) 
+Password :(blank)</t>
+  </si>
+  <si>
+    <t>Username : standard_user
+Password :(blank)</t>
+  </si>
+  <si>
+    <t>Username : (blank)
+Password : secret_sauce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Password : secret_sauce</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test Data </t>
+  </si>
+  <si>
+    <t>Username: standard_user  
+Password: secret_sauce  
+Products: Sauce Labs Backpack,Sauce Labs Bike Light, Bolt T-Shirt, Sauce Labs Fleece Jacket, Sauce Labs Onesie,Test.allTheThings() T-Shirt (Red)</t>
+  </si>
+  <si>
+    <t>Username: standard_user  
+Password: secret_sauce  
+Selected Product: Sauce Labs Backpack</t>
+  </si>
+  <si>
+    <t>Username: standard_user  
+Password: secret_sauce  
+Products: All available products</t>
+  </si>
+  <si>
+    <t>Username: standard_user  
+Password: secret_sauce  
+Product: Sauce Labs Backpack</t>
+  </si>
+  <si>
+    <t>Username: standard_user  
+Password: secret_sauce  
+Product: Sauce Labs Bike Light</t>
+  </si>
+  <si>
+    <t>Username: standard_user  
+Password: secret_sauce  
+Product: Sauce Labs Bolt T-Shirt</t>
+  </si>
+  <si>
+    <t>First Name: John  
+Last Name: Silva  
+Postal Code: 41000</t>
+  </si>
+  <si>
+    <t>First Name: (Empty)  
+Last Name: (Empty) 
+Postal Code: (Empty)</t>
+  </si>
+  <si>
+    <t>First Name: John  
+Last Name: (blank)  
+Postal Code: (blank)</t>
+  </si>
+  <si>
+    <t>Product: Sauce Labs Backpack  
+Price: $29.99</t>
+  </si>
+  <si>
+    <t>Order: 1 product (Sauce Labs Backpack)</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -471,8 +574,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -483,6 +592,12 @@
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.39997558519241921"/>
         <bgColor rgb="FFFCE5CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -523,20 +638,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -854,19 +968,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03C3DD0D-82A3-4C8A-B47B-FCE62A96A974}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.77734375" customWidth="1"/>
     <col min="2" max="2" width="20.5546875" customWidth="1"/>
-    <col min="3" max="3" width="35.21875" customWidth="1"/>
-    <col min="4" max="4" width="37.88671875" customWidth="1"/>
-    <col min="5" max="5" width="24.21875" customWidth="1"/>
-    <col min="6" max="6" width="22.77734375" customWidth="1"/>
-    <col min="7" max="7" width="12.33203125" customWidth="1"/>
+    <col min="3" max="3" width="23" customWidth="1"/>
+    <col min="4" max="4" width="35.21875" customWidth="1"/>
+    <col min="5" max="5" width="37.88671875" customWidth="1"/>
+    <col min="6" max="6" width="24.21875" customWidth="1"/>
+    <col min="7" max="7" width="22.77734375" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -874,45 +989,51 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="G2" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="H2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -920,22 +1041,25 @@
         <v>7</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -943,114 +1067,129 @@
         <v>7</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="H4" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>23</v>
       </c>
       <c r="B5" t="s">
         <v>7</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D5" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="H5" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>27</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D6" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>30</v>
-      </c>
       <c r="F6" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="H6" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>32</v>
       </c>
       <c r="B7" t="s">
         <v>7</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D7" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="F7" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="G7" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="H7" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>37</v>
       </c>
       <c r="B8" t="s">
         <v>7</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D8" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="G8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="H8" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -1058,41 +1197,45 @@
         <v>7</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="E9" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="F9" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="G9" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="H9" s="4" t="s">
         <v>13</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0221A26C-9368-47AD-B6B9-7ACAC69109FD}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5546875" customWidth="1"/>
-    <col min="2" max="2" width="21.21875" customWidth="1"/>
-    <col min="3" max="3" width="28.77734375" customWidth="1"/>
-    <col min="4" max="4" width="23.44140625" customWidth="1"/>
-    <col min="5" max="5" width="21.77734375" customWidth="1"/>
-    <col min="6" max="6" width="32.21875" customWidth="1"/>
-    <col min="7" max="7" width="25.6640625" customWidth="1"/>
+    <col min="2" max="3" width="21.21875" customWidth="1"/>
+    <col min="4" max="4" width="28.77734375" customWidth="1"/>
+    <col min="5" max="5" width="23.44140625" customWidth="1"/>
+    <col min="6" max="6" width="21.77734375" customWidth="1"/>
+    <col min="7" max="7" width="32.21875" customWidth="1"/>
+    <col min="8" max="8" width="25.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1100,22 +1243,25 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="144" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1123,22 +1269,25 @@
         <v>45</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="144" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="144" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1146,22 +1295,28 @@
         <v>50</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="J3" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -1169,18 +1324,21 @@
         <v>50</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="H4" s="4" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1192,18 +1350,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{941D7F56-0A66-45F9-9411-6368C0E57E42}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.88671875" customWidth="1"/>
-    <col min="2" max="2" width="21.21875" customWidth="1"/>
-    <col min="3" max="4" width="21.33203125" customWidth="1"/>
-    <col min="5" max="5" width="20.109375" customWidth="1"/>
-    <col min="6" max="6" width="21" customWidth="1"/>
-    <col min="7" max="7" width="14.109375" customWidth="1"/>
+    <col min="2" max="3" width="21.21875" customWidth="1"/>
+    <col min="4" max="5" width="21.33203125" customWidth="1"/>
+    <col min="6" max="6" width="20.109375" customWidth="1"/>
+    <col min="7" max="7" width="21" customWidth="1"/>
+    <col min="8" max="8" width="14.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>59</v>
       </c>
@@ -1211,22 +1369,25 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1234,22 +1395,25 @@
         <v>60</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="144" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="144" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1257,22 +1421,25 @@
         <v>60</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -1280,18 +1447,21 @@
         <v>60</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="H4" s="4" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1302,19 +1472,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78991AA3-78FA-4E16-8470-0F09F39BEC28}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.6640625" customWidth="1"/>
-    <col min="2" max="2" width="20.33203125" customWidth="1"/>
-    <col min="3" max="3" width="25.6640625" customWidth="1"/>
-    <col min="4" max="4" width="23.33203125" customWidth="1"/>
-    <col min="5" max="5" width="24.77734375" customWidth="1"/>
-    <col min="6" max="6" width="20.88671875" customWidth="1"/>
-    <col min="7" max="7" width="12.6640625" customWidth="1"/>
+    <col min="2" max="3" width="20.33203125" customWidth="1"/>
+    <col min="4" max="4" width="25.6640625" customWidth="1"/>
+    <col min="5" max="5" width="23.33203125" customWidth="1"/>
+    <col min="6" max="6" width="24.77734375" customWidth="1"/>
+    <col min="7" max="7" width="20.88671875" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>59</v>
       </c>
@@ -1322,22 +1492,25 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1345,22 +1518,25 @@
         <v>73</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1368,45 +1544,51 @@
         <v>73</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
       <c r="B4" t="s">
         <v>73</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D4" t="s">
         <v>82</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="H4" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -1414,22 +1596,25 @@
         <v>73</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="H5" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -1437,22 +1622,25 @@
         <v>90</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="H6" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>32</v>
       </c>
@@ -1460,45 +1648,52 @@
         <v>90</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="F7" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="G7" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="H7" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>37</v>
       </c>
       <c r="B8" t="s">
         <v>99</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D8" t="s">
         <v>100</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="G8" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="H8" s="4" t="s">
         <v>13</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>